--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55966A5-501D-4205-94BE-362A69654B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048BE640-24C1-4033-924E-AEF9000055AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="136">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -634,6 +634,156 @@
   <si>
     <t>General feedback: share best practices and lessons learned when you learn something
 For any question regarding the stacks please reach out to Anar:Anar.Akhmedov@infineon.com</t>
+  </si>
+  <si>
+    <t>04.09.2026</t>
+  </si>
+  <si>
+    <t>Christelle: very well explained and good homepage thanks</t>
+  </si>
+  <si>
+    <t>Mariata: maybe you can be more specific on your homepage what you mean with backend</t>
+  </si>
+  <si>
+    <t>Ben: good homepage but your voice was very low</t>
+  </si>
+  <si>
+    <t>Esther: On Project / Task be more specific wht it is … not veery reader knows what Taks 1-3; good voice &amp; good homepage</t>
+  </si>
+  <si>
+    <t>Phares: good homepage and good voice</t>
+  </si>
+  <si>
+    <t>Madiega: be more specific project task on what you are working on</t>
+  </si>
+  <si>
+    <t>Tania: good homepage and good voice</t>
+  </si>
+  <si>
+    <t>Carine:
+Not in the call</t>
+  </si>
+  <si>
+    <t>Rayanne:
+Not in the call</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>General Feedback</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinate with the other team members</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Make sure you communicate and coordinate with the people working on the other parts of the project, especially the backend team. The goal is to ensure that your module can be smoothly integrated into the final product without compatibility or integration issues.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explain all abbreviations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Whenever you use an abbreviation or acronym on your homepage, always provide its full meaning the first time you mention it. This ensures that anyone viewing your homepage can understand the content, even if they are not familiar with the terminology.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Clearly introduce your module</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+At the beginning of your presentation, clearly state which module you are working on and briefly explain its purpose. This will help everyone understand the context of your presentation from the start.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Questions about the tech stack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+If you have any questions or need clarification regarding the technology stack, frameworks, or tools being used, please reach out to Anar for guidance:Anar.Akhmedov@infineon.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Hans and Anar</t>
   </si>
 </sst>
 </file>
@@ -809,7 +959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -887,6 +1037,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1734,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -3698,6 +3849,272 @@
       </c>
       <c r="G89" s="22"/>
       <c r="H89" s="22"/>
+    </row>
+    <row r="90" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="8">
+        <v>8</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="14"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
+        <v>1</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="18"/>
+      <c r="H92" s="19"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="21">
+        <v>2</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C93" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D93" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="21">
+        <v>3</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="21">
+        <v>4</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D95" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="22"/>
+      <c r="H95" s="22"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="21">
+        <v>5</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="22"/>
+      <c r="H96" s="22"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" s="21">
+        <v>6</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C97" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" s="21">
+        <v>7</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C98" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="21">
+        <v>8</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C99" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D99" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="22"/>
+      <c r="H99" s="22"/>
+    </row>
+    <row r="100" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="21">
+        <v>9</v>
+      </c>
+      <c r="B100" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C100" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="22"/>
+      <c r="H100" s="22"/>
+    </row>
+    <row r="101" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="21">
+        <v>10</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D101" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3717,7 +4134,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -3904,18 +4321,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3935,18 +4352,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048BE640-24C1-4033-924E-AEF9000055AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E58BEE5-D0E2-4976-81CC-ED6DEAE80FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="147">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -784,6 +784,136 @@
   </si>
   <si>
     <t>Hans and Anar</t>
+  </si>
+  <si>
+    <t>11.09.2026</t>
+  </si>
+  <si>
+    <t>Esther: get well soon</t>
+  </si>
+  <si>
+    <t>Mariata: all good; what are all pages </t>
+  </si>
+  <si>
+    <t>Carine: all good – will explained by using the word “Visitor management”, it is
+ well understood what it is all about:</t>
+  </si>
+  <si>
+    <t>Madiega: all good – what is a Spring Boot
+make sure evrything works</t>
+  </si>
+  <si>
+    <t>Rayanne: your voice was a bit low, about what machinery you are talking of
+your backend looks more mature now</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>General Feedback</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinate with the other team members</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Make sure you communicate and coordinate with the people working on the other parts of the project, especially the backend team. The goal is to ensure that your module can be smoothly integrated into the final product without compatibility or integration issues.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explain all abbreviations technical terms and tools</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Whenever you use an abbreviation or acronym, technical term, framework, or tool on your homepage, always provide its full meaning the first time you mention it. This ensures that anyone viewing your homepage can understand the content, even if they are not familiar with the terminology.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Clearly introduce your module</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+At the beginning of your presentation, clearly state which module you are working on and briefly explain its purpose. This will help everyone understand the context of your presentation from the start.</t>
+    </r>
+  </si>
+  <si>
+    <t>Abdoul: all good thanks
+Make sure the final result aligns with the defined KPIs (Key Performance Indicators) and meets the expected objectives.</t>
+  </si>
+  <si>
+    <t>Phares: all good thanks
+Before adding the remaining features, make sure that everything currently implemented works correctly. Test the existing functionality and resolve any issues before moving forward. This will help ensure a stable and reliable final module.</t>
+  </si>
+  <si>
+    <t>Christelle: all good what are your sensors actually measuring; good Logo but 
+maybe storing Mangos would be an even better picture add more 
+Expand your backend by adding more entities (the different types of data or objects in your system) and relationships (the connections between them).</t>
+  </si>
+  <si>
+    <t>Tania: all good; what security do you mean – security of access  
+Make sure to test the entire workflow from start to finish, ensuring that all components work together correctly.</t>
   </si>
 </sst>
 </file>
@@ -959,7 +1089,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,13 +1161,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1885,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -1897,16 +2030,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
@@ -3925,7 +4058,7 @@
       <c r="B93" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C93" s="27" t="s">
+      <c r="C93" s="25" t="s">
         <v>125</v>
       </c>
       <c r="D93" s="22" t="s">
@@ -3947,7 +4080,7 @@
       <c r="B94" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C94" s="27" t="s">
+      <c r="C94" s="25" t="s">
         <v>126</v>
       </c>
       <c r="D94" s="22" t="s">
@@ -3969,7 +4102,7 @@
       <c r="B95" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C95" s="27" t="s">
+      <c r="C95" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D95" s="22" t="s">
@@ -3991,7 +4124,7 @@
       <c r="B96" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C96" s="27" t="s">
+      <c r="C96" s="25" t="s">
         <v>128</v>
       </c>
       <c r="D96" s="22" t="s">
@@ -4013,7 +4146,7 @@
       <c r="B97" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C97" s="27" t="s">
+      <c r="C97" s="25" t="s">
         <v>129</v>
       </c>
       <c r="D97" s="22" t="s">
@@ -4035,7 +4168,7 @@
       <c r="B98" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C98" s="27" t="s">
+      <c r="C98" s="25" t="s">
         <v>130</v>
       </c>
       <c r="D98" s="22" t="s">
@@ -4057,7 +4190,7 @@
       <c r="B99" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C99" s="27" t="s">
+      <c r="C99" s="25" t="s">
         <v>131</v>
       </c>
       <c r="D99" s="22" t="s">
@@ -4115,6 +4248,272 @@
       </c>
       <c r="G101" s="22"/>
       <c r="H101" s="22"/>
+    </row>
+    <row r="102" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A102" s="8">
+        <v>9</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="12"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="14"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="232" x14ac:dyDescent="0.35">
+      <c r="A104" s="1">
+        <v>1</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" s="18"/>
+      <c r="H104" s="19"/>
+    </row>
+    <row r="105" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="21">
+        <v>2</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" s="22"/>
+      <c r="H105" s="22"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" s="21">
+        <v>3</v>
+      </c>
+      <c r="B106" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" s="22"/>
+      <c r="H106" s="22"/>
+    </row>
+    <row r="107" spans="1:8" ht="63.5" x14ac:dyDescent="0.35">
+      <c r="A107" s="21">
+        <v>4</v>
+      </c>
+      <c r="B107" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22"/>
+    </row>
+    <row r="108" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="21">
+        <v>5</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" s="22"/>
+      <c r="H108" s="22"/>
+    </row>
+    <row r="109" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="A109" s="21">
+        <v>6</v>
+      </c>
+      <c r="B109" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C109" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" s="22"/>
+      <c r="H109" s="22"/>
+    </row>
+    <row r="110" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="21">
+        <v>7</v>
+      </c>
+      <c r="B110" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D110" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E110" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22"/>
+    </row>
+    <row r="111" spans="1:8" ht="76" x14ac:dyDescent="0.35">
+      <c r="A111" s="21">
+        <v>8</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D111" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" s="22"/>
+      <c r="H111" s="22"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" s="21">
+        <v>9</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D112" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E112" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" s="22"/>
+      <c r="H112" s="22"/>
+    </row>
+    <row r="113" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="21">
+        <v>10</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D113" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" s="22"/>
+      <c r="H113" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4134,7 +4533,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -4154,16 +4553,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -4321,18 +4720,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4352,18 +4751,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E58BEE5-D0E2-4976-81CC-ED6DEAE80FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1EEAFB-3025-423E-8858-A00D2E10B426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="158">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -914,6 +914,84 @@
   <si>
     <t>Tania: all good; what security do you mean – security of access  
 Make sure to test the entire workflow from start to finish, ensuring that all components work together correctly.</t>
+  </si>
+  <si>
+    <t>Mariata: very good presentation, organized updates – where is the API data coming from?</t>
+  </si>
+  <si>
+    <t>Ben: very good presentation, organized updates – very good that you
+ managed to meet an expert regarding product transformation, it is 
+always useful to get hands-on and real-world insights</t>
+  </si>
+  <si>
+    <t>Phares: get well soon</t>
+  </si>
+  <si>
+    <t>Rayane: very good presentation, organized updates – clear progress and next steps – are you considering input from other modules e.g. plants to estimate expected load</t>
+  </si>
+  <si>
+    <t>Justine: very good presentation, organized updates – how will your BE integrate input from other module e.g. equipment energy consumption and make forecasting</t>
+  </si>
+  <si>
+    <t>Carine: very good presentation, organized updates – clear next steps as well</t>
+  </si>
+  <si>
+    <t>Christelle: get well soon</t>
+  </si>
+  <si>
+    <t>Tania: very good presentation, organized updates – clear next steps and aligned with the plan</t>
+  </si>
+  <si>
+    <t>Esther: very good presentation, organized updates – how to prepare input to all other modules based on amount of mango harvested for e.g.</t>
+  </si>
+  <si>
+    <t>Abdo and Anar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>General Feedback</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinate with the other team members</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Make sure you communicate and coordinate with the people working on the other parts of the project, especially the backend team. The goal is to ensure that your module can be smoothly integrated into the final product without compatibility or integration issues..</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1162,14 +1240,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2018,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -2030,16 +2108,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
@@ -4324,7 +4402,7 @@
       <c r="B105" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C105" s="28" t="s">
+      <c r="C105" s="26" t="s">
         <v>143</v>
       </c>
       <c r="D105" s="22" t="s">
@@ -4368,7 +4446,7 @@
       <c r="B107" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C107" s="28" t="s">
+      <c r="C107" s="26" t="s">
         <v>144</v>
       </c>
       <c r="D107" s="22" t="s">
@@ -4390,7 +4468,7 @@
       <c r="B108" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C108" s="28" t="s">
+      <c r="C108" s="26" t="s">
         <v>141</v>
       </c>
       <c r="D108" s="22" t="s">
@@ -4412,7 +4490,7 @@
       <c r="B109" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="28" t="s">
+      <c r="C109" s="26" t="s">
         <v>140</v>
       </c>
       <c r="D109" s="22" t="s">
@@ -4434,7 +4512,7 @@
       <c r="B110" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C110" s="28" t="s">
+      <c r="C110" s="26" t="s">
         <v>139</v>
       </c>
       <c r="D110" s="22" t="s">
@@ -4456,7 +4534,7 @@
       <c r="B111" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C111" s="28" t="s">
+      <c r="C111" s="26" t="s">
         <v>145</v>
       </c>
       <c r="D111" s="22" t="s">
@@ -4514,6 +4592,272 @@
       </c>
       <c r="G113" s="22"/>
       <c r="H113" s="22"/>
+    </row>
+    <row r="114" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="8">
+        <v>9</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="12"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="14"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A116" s="1">
+        <v>1</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" s="18"/>
+      <c r="H116" s="19"/>
+    </row>
+    <row r="117" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="A117" s="21">
+        <v>2</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
+    </row>
+    <row r="118" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A118" s="21">
+        <v>3</v>
+      </c>
+      <c r="B118" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C118" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119" s="21">
+        <v>4</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C119" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" s="22"/>
+      <c r="H119" s="22"/>
+    </row>
+    <row r="120" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A120" s="21">
+        <v>5</v>
+      </c>
+      <c r="B120" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C120" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" s="22"/>
+      <c r="H120" s="22"/>
+    </row>
+    <row r="121" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A121" s="21">
+        <v>6</v>
+      </c>
+      <c r="B121" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C121" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" s="22"/>
+      <c r="H121" s="22"/>
+    </row>
+    <row r="122" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="A122" s="21">
+        <v>7</v>
+      </c>
+      <c r="B122" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E122" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A123" s="21">
+        <v>8</v>
+      </c>
+      <c r="B123" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C123" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
+    </row>
+    <row r="124" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="21">
+        <v>9</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C124" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E124" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" s="22"/>
+      <c r="H124" s="22"/>
+    </row>
+    <row r="125" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="21">
+        <v>10</v>
+      </c>
+      <c r="B125" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4533,7 +4877,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -4553,16 +4897,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -4720,18 +5064,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4751,18 +5095,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1EEAFB-3025-423E-8858-A00D2E10B426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A8A7EF-A157-4AD3-A3E2-D2171D31F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="168">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -992,6 +992,42 @@
       <t xml:space="preserve">
 Make sure you communicate and coordinate with the people working on the other parts of the project, especially the backend team. The goal is to ensure that your module can be smoothly integrated into the final product without compatibility or integration issues..</t>
     </r>
+  </si>
+  <si>
+    <t>Phares: Coordinate with the other team members and have them review your work to ensure everything works correctly. Also, update the calendar week/date on your homepage, as it is currently out of date.</t>
+  </si>
+  <si>
+    <t>Rayane: Clearly define how spare parts are linked to the other entities/modules.</t>
+  </si>
+  <si>
+    <t>Christelle: Not in the call</t>
+  </si>
+  <si>
+    <t>Anar</t>
+  </si>
+  <si>
+    <t>Esther: Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
+  </si>
+  <si>
+    <t>Marieta:Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
+  </si>
+  <si>
+    <t>Carine:Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
+  </si>
+  <si>
+    <t>Tania: Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
+  </si>
+  <si>
+    <t>Justine: Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
+  </si>
+  <si>
+    <t>Abdoul:Coordinate with the other team members and have them review your work to
+  ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -4595,7 +4631,7 @@
     </row>
     <row r="114" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>136</v>
@@ -4858,6 +4894,272 @@
       </c>
       <c r="G125" s="22"/>
       <c r="H125" s="22"/>
+    </row>
+    <row r="126" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="8">
+        <v>11</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="12"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="14"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A128" s="1">
+        <v>1</v>
+      </c>
+      <c r="B128" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" s="18"/>
+      <c r="H128" s="19"/>
+    </row>
+    <row r="129" spans="1:8" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A129" s="21">
+        <v>2</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C129" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E129" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22"/>
+    </row>
+    <row r="130" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+      <c r="A130" s="21">
+        <v>3</v>
+      </c>
+      <c r="B130" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E130" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" s="22"/>
+      <c r="H130" s="22"/>
+    </row>
+    <row r="131" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A131" s="21">
+        <v>4</v>
+      </c>
+      <c r="B131" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C131" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E131" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" s="22"/>
+      <c r="H131" s="22"/>
+    </row>
+    <row r="132" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A132" s="21">
+        <v>5</v>
+      </c>
+      <c r="B132" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C132" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E132" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+    </row>
+    <row r="133" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A133" s="21">
+        <v>6</v>
+      </c>
+      <c r="B133" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+    </row>
+    <row r="134" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A134" s="21">
+        <v>7</v>
+      </c>
+      <c r="B134" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E134" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" s="22"/>
+      <c r="H134" s="22"/>
+    </row>
+    <row r="135" spans="1:8" ht="51" x14ac:dyDescent="0.35">
+      <c r="A135" s="21">
+        <v>8</v>
+      </c>
+      <c r="B135" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E135" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" s="22"/>
+      <c r="H135" s="22"/>
+    </row>
+    <row r="136" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A136" s="21">
+        <v>9</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" s="22"/>
+      <c r="H136" s="22"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A137" s="21">
+        <v>10</v>
+      </c>
+      <c r="B137" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C137" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G137" s="22"/>
+      <c r="H137" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4876,8 +5178,8 @@
       <formula>"open"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5064,18 +5366,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5095,18 +5397,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A8A7EF-A157-4AD3-A3E2-D2171D31F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567CCBD-CBEC-4EFE-8F53-FCD1704B843B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="181">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -1029,12 +1029,217 @@
     <t>Abdoul:Coordinate with the other team members and have them review your work to
   ensure everything works correctly and would work smoothly with the other modules before final integration.</t>
   </si>
+  <si>
+    <t>18.09.2026</t>
+  </si>
+  <si>
+    <t>25.09.2026</t>
+  </si>
+  <si>
+    <t>02.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Excellence program Students , Tim  ,  Wilfried , .</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Justine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Your homepage update section contains too much text. Summarize the main achievements and explain them briefly and concisely.: Coordinate with the other team members and have them review your work to ensure everything works correctly. Also, update the calendar week/date on your homepage, as it is currently out of date.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Phares</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Good job resolving the conflict on GitHub. Continue progressing proactively without waiting for feedback before moving forward.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tania</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Your presentation was brief. Go deeper into your tasks, progress, and achievements.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Abdoul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:Continue progressing with your work without being dependent on feedback from your teammates before moving forward.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Marieta:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CAbdoul:Continue progressing with your work without being dependent on feedback from your teammates before moving forward.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Christelle:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Continue progressing with your work without being dependent on feedback.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Rayane: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">not in the call </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Carine:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> not in the call</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Esther</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Continue progressing with your work without being dependent on feedback from your teammates before moving forward.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1097,6 +1302,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2132,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -4634,7 +4846,7 @@
         <v>10</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>70</v>
@@ -4900,7 +5112,7 @@
         <v>11</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>70</v>
@@ -5160,6 +5372,272 @@
       </c>
       <c r="G137" s="22"/>
       <c r="H137" s="22"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A138" s="8">
+        <v>12</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="12"/>
+      <c r="G138" s="13"/>
+      <c r="H138" s="14"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A139" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G139" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A140" s="1">
+        <v>1</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E140" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G140" s="18"/>
+      <c r="H140" s="19"/>
+    </row>
+    <row r="141" spans="1:8" ht="64" x14ac:dyDescent="0.35">
+      <c r="A141" s="21">
+        <v>2</v>
+      </c>
+      <c r="B141" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C141" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" s="22"/>
+      <c r="H141" s="22"/>
+    </row>
+    <row r="142" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A142" s="21">
+        <v>3</v>
+      </c>
+      <c r="B142" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C142" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22"/>
+    </row>
+    <row r="143" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A143" s="21">
+        <v>4</v>
+      </c>
+      <c r="B143" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C143" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22"/>
+    </row>
+    <row r="144" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A144" s="21">
+        <v>5</v>
+      </c>
+      <c r="B144" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C144" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" s="22"/>
+      <c r="H144" s="22"/>
+    </row>
+    <row r="145" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="21">
+        <v>6</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C145" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22"/>
+    </row>
+    <row r="146" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A146" s="21">
+        <v>7</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C146" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22"/>
+    </row>
+    <row r="147" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A147" s="21">
+        <v>8</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C147" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" s="21">
+        <v>9</v>
+      </c>
+      <c r="B148" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E148" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" s="21">
+        <v>10</v>
+      </c>
+      <c r="B149" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G149" s="22"/>
+      <c r="H149" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -5179,7 +5657,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137 F140:F149" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5366,18 +5844,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5397,18 +5875,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567CCBD-CBEC-4EFE-8F53-FCD1704B843B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89C3969-AEAC-4E88-A46D-B4283B855158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="191">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -1233,6 +1233,193 @@
       </rPr>
       <t>: Continue progressing with your work without being dependent on feedback from your teammates before moving forward.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Excellence program Students , Tim  ,  Wilfried ,Linus .</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abdoul: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>great work on cross module testing</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Esther: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>very good progress</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tania: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>thanks for the update; next week feel free to go into some more details on your progress as well as integration with other modules</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Phares:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Good progress overall, but please speak a little louder </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nd more clearly, as you were sometimes difficult to hear.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Justine: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>thanks for the great progress update</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Christelle: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>great presentation; ensure close coordination with all dependent module owners</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Mariata: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>thanks for the update; next week feel free to elaborate more on specific advancements and make written</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> progress report less </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>generic</t>
+    </r>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Tim</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1602,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1496,6 +1683,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2344,7 +2534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -5638,6 +5828,272 @@
       </c>
       <c r="G149" s="22"/>
       <c r="H149" s="22"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" s="8">
+        <v>13</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="12"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="14"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E151" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A152" s="1">
+        <v>1</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E152" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G152" s="18"/>
+      <c r="H152" s="19"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" s="21">
+        <v>2</v>
+      </c>
+      <c r="B153" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C153" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G153" s="22"/>
+      <c r="H153" s="22"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154" s="21">
+        <v>3</v>
+      </c>
+      <c r="B154" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E154" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G154" s="22"/>
+      <c r="H154" s="22"/>
+    </row>
+    <row r="155" spans="1:8" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="21">
+        <v>4</v>
+      </c>
+      <c r="B155" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C155" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" s="22"/>
+      <c r="H155" s="22"/>
+    </row>
+    <row r="156" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A156" s="21">
+        <v>5</v>
+      </c>
+      <c r="B156" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C156" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" s="22"/>
+      <c r="H156" s="22"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="21">
+        <v>6</v>
+      </c>
+      <c r="B157" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C157" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" s="22"/>
+      <c r="H157" s="22"/>
+    </row>
+    <row r="158" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A158" s="21">
+        <v>7</v>
+      </c>
+      <c r="B158" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C158" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E158" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G158" s="22"/>
+      <c r="H158" s="22"/>
+    </row>
+    <row r="159" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A159" s="21">
+        <v>8</v>
+      </c>
+      <c r="B159" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C159" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G159" s="22"/>
+      <c r="H159" s="22"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="21">
+        <v>9</v>
+      </c>
+      <c r="B160" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C160" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G160" s="22"/>
+      <c r="H160" s="22"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A161" s="21">
+        <v>10</v>
+      </c>
+      <c r="B161" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C161" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G161" s="22"/>
+      <c r="H161" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -5657,7 +6113,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137 F140:F149" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137 F140:F149 F152:F161" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -5844,18 +6300,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5875,18 +6331,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MoM_Excellence_program2026.xlsx
+++ b/MoM_Excellence_program2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Excellence_Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89C3969-AEAC-4E88-A46D-B4283B855158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC69E148-DE31-4B46-92D5-D27DDED039B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="201">
   <si>
     <t>Meeting Minutes</t>
   </si>
@@ -1420,6 +1420,278 @@
   </si>
   <si>
     <t>Tim</t>
+  </si>
+  <si>
+    <t>Hans Ehm, Abdelgafar Ismail, Excellence program Students , Botho Schanze, Tim , Hans ,  Wilfried , Anar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Christelle:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>good homepage, good voice, good links – looking forward to the crop storage pages</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>very good updates, and good job connecting to team members, if help is needed regarding bugs check if Anar can help</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Esther: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Very good updates, and great that you implemented feedback from Tim
+Good voice overall. Consider changing the text color across all entries to improve readability. Looking forward to seeing your work integrated with the other modules.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phares: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>very good updates, it seems you already in the integration phase, means BE is done that is great</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Good voice. On your homepage, please remove any bullet points that do not contain any content to keep the page clean and professional</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Abdoul: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>We couldn’t hear you during the presentation, but your homepage looks good overall</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Mariata: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>not in the call</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Justine: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>not in the call</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tania: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>not in the call</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>General Feedback</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Business Model Canvas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Prepare for this week's brainstorming session on the Business Model Canvas. A draft Business Model Canvas is available on Miro for review beforehand.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Project Alignment Meeting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> We should schedule a meeting to align on the project’s direction and next steps. Let’s revisit the initial 12-week plan and assess how many additional weeks we may need to complete the project.
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Focus on improving communication and collaboration across the team to ensure a more connected and coordinated approach.</t>
+    </r>
+  </si>
+  <si>
+    <t>16.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1678,14 +1950,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2534,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.453125" style="4" customWidth="1"/>
@@ -2546,16 +2818,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
@@ -5904,7 +6176,7 @@
       <c r="B153" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C153" s="29" t="s">
+      <c r="C153" s="27" t="s">
         <v>182</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -6094,6 +6366,272 @@
       </c>
       <c r="G161" s="22"/>
       <c r="H161" s="22"/>
+    </row>
+    <row r="162" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A162" s="8">
+        <v>14</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="12"/>
+      <c r="G162" s="13"/>
+      <c r="H162" s="14"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E163" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G163" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A164" s="1">
+        <v>1</v>
+      </c>
+      <c r="B164" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E164" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G164" s="18"/>
+      <c r="H164" s="19"/>
+    </row>
+    <row r="165" spans="1:8" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A165" s="21">
+        <v>2</v>
+      </c>
+      <c r="B165" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" s="22"/>
+      <c r="H165" s="22"/>
+    </row>
+    <row r="166" spans="1:8" ht="64" x14ac:dyDescent="0.35">
+      <c r="A166" s="21">
+        <v>3</v>
+      </c>
+      <c r="B166" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C166" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G166" s="22"/>
+      <c r="H166" s="22"/>
+    </row>
+    <row r="167" spans="1:8" ht="65" x14ac:dyDescent="0.35">
+      <c r="A167" s="21">
+        <v>4</v>
+      </c>
+      <c r="B167" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C167" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+    </row>
+    <row r="168" spans="1:8" ht="52" x14ac:dyDescent="0.35">
+      <c r="A168" s="21">
+        <v>5</v>
+      </c>
+      <c r="B168" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C168" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G168" s="22"/>
+      <c r="H168" s="22"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="21">
+        <v>6</v>
+      </c>
+      <c r="B169" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G169" s="22"/>
+      <c r="H169" s="22"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="21">
+        <v>7</v>
+      </c>
+      <c r="B170" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C170" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G170" s="22"/>
+      <c r="H170" s="22"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="21">
+        <v>8</v>
+      </c>
+      <c r="B171" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C171" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G171" s="22"/>
+      <c r="H171" s="22"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="21">
+        <v>9</v>
+      </c>
+      <c r="B172" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C172" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G172" s="22"/>
+      <c r="H172" s="22"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="21">
+        <v>10</v>
+      </c>
+      <c r="B173" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C173" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" s="22"/>
+      <c r="H173" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -6113,7 +6651,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137 F140:F149 F152:F161" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F17 F20:F29 F32:F41 F44:F53 F56:F65 F68:F77 F80:F89 F92:F101 F104:F113 F116:F125 F128:F137 F140:F149 F152:F161 F164:F173" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Status</formula1>
     </dataValidation>
   </dataValidations>
@@ -6133,16 +6671,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -6300,18 +6838,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6331,18 +6869,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099BC07E-159D-4A16-BA20-897EF5E09C4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796D9FC9-4B98-4FFD-BB78-C2E8DE274F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>